--- a/data/metas_gdr.xlsx
+++ b/data/metas_gdr.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsalcedo\Desktop\ITP\GDR - NUEVO\Automatización GDR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E900F7C-8965-46E3-8C99-D561EE7D9D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0008187-725B-480F-B96A-6E6B1969BC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A49B71B2-14C1-4C12-8BB4-4404E18A9970}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,9 +44,6 @@
     <t>CITE</t>
   </si>
   <si>
-    <t>CITE Acuicola Puno</t>
-  </si>
-  <si>
     <t>CITEagroindustrial Chavimochic</t>
   </si>
   <si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>Meta Indicador 3</t>
+  </si>
+  <si>
+    <t>CITEacuícola Puno</t>
   </si>
 </sst>
 </file>
@@ -488,24 +491,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A79AF-49CF-4970-97EB-183FBA01179C}">
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>103</v>
@@ -519,7 +525,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>224</v>
@@ -533,7 +539,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>367</v>
@@ -547,7 +553,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>264</v>
@@ -561,7 +567,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>371</v>
@@ -575,7 +581,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>106</v>
@@ -589,7 +595,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>681</v>
@@ -603,7 +609,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>200</v>
@@ -617,7 +623,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>66</v>
@@ -631,7 +637,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <v>215</v>
@@ -645,7 +651,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>124</v>
@@ -659,7 +665,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>207</v>
@@ -673,7 +679,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>186</v>
@@ -687,7 +693,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>313</v>
@@ -701,7 +707,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>306</v>
@@ -715,7 +721,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>203</v>
@@ -729,7 +735,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>196</v>
@@ -743,7 +749,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>257</v>
@@ -757,7 +763,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
         <v>129</v>
@@ -771,7 +777,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
         <v>311</v>
@@ -785,7 +791,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3">
         <v>193</v>
@@ -799,7 +805,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>69</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
         <v>189</v>
@@ -830,10 +836,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="C25" s="2">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1">
         <v>0.3</v>
@@ -841,19 +847,24 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="3">
-        <v>57</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="D26" s="1">
         <v>0.3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{320A79AF-49CF-4970-97EB-183FBA01179C}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D26">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
